--- a/backend/storage/imports/Master_SBM/Honorarium 39 SATUAN BIAYA KONSUMSI KEGIATAN PENDIDIKAN DAN PELATIHAN (DIKLAT).xlsx
+++ b/backend/storage/imports/Master_SBM/Honorarium 39 SATUAN BIAYA KONSUMSI KEGIATAN PENDIDIKAN DAN PELATIHAN (DIKLAT).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\imports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93DC2B5-68F7-401E-9CB1-BD917CE7C671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB62C089-892E-40F1-B394-5BDB2E463E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{739865E5-A0EC-44F1-B7B0-47122DB504AA}"/>
   </bookViews>
@@ -313,12 +313,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -330,27 +327,18 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
@@ -362,6 +350,15 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -686,64 +683,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1">
+      <c r="A1" s="15">
         <v>39</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>-1</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>-2</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>-3</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>-4</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>-5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+      <c r="A4" s="13">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6">
         <v>41000</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="6">
         <v>17000</v>
       </c>
     </row>
@@ -751,16 +748,16 @@
       <c r="A5" s="9">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="11">
+      <c r="C5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="8">
         <v>38000</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="8">
         <v>14000</v>
       </c>
     </row>
@@ -768,16 +765,16 @@
       <c r="A6" s="9">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="11">
+      <c r="C6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8">
         <v>42000</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="8">
         <v>15000</v>
       </c>
     </row>
@@ -785,16 +782,16 @@
       <c r="A7" s="9">
         <v>4</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="11">
+      <c r="C7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="8">
         <v>36000</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="8">
         <v>20000</v>
       </c>
     </row>
@@ -802,16 +799,16 @@
       <c r="A8" s="9">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="11">
+      <c r="C8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="8">
         <v>43000</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="8">
         <v>15000</v>
       </c>
     </row>
@@ -819,16 +816,16 @@
       <c r="A9" s="9">
         <v>6</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="11">
+      <c r="C9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="8">
         <v>36000</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <v>15000</v>
       </c>
     </row>
@@ -836,16 +833,16 @@
       <c r="A10" s="9">
         <v>7</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="11">
+      <c r="C10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="8">
         <v>51000</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="8">
         <v>15000</v>
       </c>
     </row>
@@ -853,16 +850,16 @@
       <c r="A11" s="9">
         <v>8</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="11">
+      <c r="C11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="8">
         <v>35000</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="8">
         <v>17000</v>
       </c>
     </row>
@@ -870,16 +867,16 @@
       <c r="A12" s="9">
         <v>9</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="C12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="8">
         <v>39000</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="8">
         <v>13000</v>
       </c>
     </row>
@@ -887,16 +884,16 @@
       <c r="A13" s="9">
         <v>10</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="11">
+      <c r="C13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="8">
         <v>37000</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="8">
         <v>16000</v>
       </c>
     </row>
@@ -904,16 +901,16 @@
       <c r="A14" s="9">
         <v>11</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="11">
+      <c r="C14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="8">
         <v>44000</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="8">
         <v>17000</v>
       </c>
     </row>
@@ -921,16 +918,16 @@
       <c r="A15" s="9">
         <v>12</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="11">
+      <c r="C15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8">
         <v>43000</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="8">
         <v>18000</v>
       </c>
     </row>
@@ -938,16 +935,16 @@
       <c r="A16" s="9">
         <v>13</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="11">
+      <c r="C16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="8">
         <v>45000</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="8">
         <v>20000</v>
       </c>
     </row>
@@ -955,16 +952,16 @@
       <c r="A17" s="9">
         <v>14</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="11">
+      <c r="C17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="8">
         <v>55000</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="8">
         <v>14000</v>
       </c>
     </row>
@@ -972,16 +969,16 @@
       <c r="A18" s="9">
         <v>15</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="11">
+      <c r="C18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="8">
         <v>47000</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="8">
         <v>14000</v>
       </c>
     </row>
@@ -989,16 +986,16 @@
       <c r="A19" s="9">
         <v>16</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="11">
+      <c r="C19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="8">
         <v>40000</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="8">
         <v>19000</v>
       </c>
     </row>
@@ -1006,16 +1003,16 @@
       <c r="A20" s="9">
         <v>17</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="11">
+      <c r="C20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="8">
         <v>41000</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="8">
         <v>18000</v>
       </c>
     </row>
@@ -1023,16 +1020,16 @@
       <c r="A21" s="9">
         <v>18</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="11">
+      <c r="C21" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="8">
         <v>41000</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="8">
         <v>15000</v>
       </c>
     </row>
@@ -1040,16 +1037,16 @@
       <c r="A22" s="9">
         <v>19</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="11">
+      <c r="C22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="8">
         <v>42000</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="8">
         <v>18000</v>
       </c>
     </row>
@@ -1057,16 +1054,16 @@
       <c r="A23" s="9">
         <v>20</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="11">
+      <c r="C23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="8">
         <v>41000</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="8">
         <v>14000</v>
       </c>
     </row>
@@ -1074,16 +1071,16 @@
       <c r="A24" s="9">
         <v>21</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="11">
+      <c r="C24" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="8">
         <v>34000</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="8">
         <v>13000</v>
       </c>
     </row>
@@ -1091,16 +1088,16 @@
       <c r="A25" s="9">
         <v>22</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="11">
+      <c r="C25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="8">
         <v>41000</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="8">
         <v>15000</v>
       </c>
     </row>
@@ -1108,16 +1105,16 @@
       <c r="A26" s="9">
         <v>23</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="11">
+      <c r="C26" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="8">
         <v>39000</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="8">
         <v>22000</v>
       </c>
     </row>
@@ -1125,16 +1122,16 @@
       <c r="A27" s="9">
         <v>24</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="11">
+      <c r="C27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="8">
         <v>43000</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="8">
         <v>18000</v>
       </c>
     </row>
@@ -1142,16 +1139,16 @@
       <c r="A28" s="9">
         <v>25</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="11">
+      <c r="C28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="8">
         <v>47000</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="8">
         <v>22000</v>
       </c>
     </row>
@@ -1159,16 +1156,16 @@
       <c r="A29" s="9">
         <v>26</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="11">
+      <c r="C29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="8">
         <v>36000</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="8">
         <v>13000</v>
       </c>
     </row>
@@ -1176,16 +1173,16 @@
       <c r="A30" s="9">
         <v>27</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="11">
+      <c r="C30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="8">
         <v>44000</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="8">
         <v>18000</v>
       </c>
     </row>
@@ -1193,16 +1190,16 @@
       <c r="A31" s="9">
         <v>28</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="11">
+      <c r="C31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="8">
         <v>48000</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="8">
         <v>21000</v>
       </c>
     </row>
@@ -1210,16 +1207,16 @@
       <c r="A32" s="9">
         <v>29</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="11">
+      <c r="C32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="8">
         <v>39000</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="8">
         <v>15000</v>
       </c>
     </row>
@@ -1227,16 +1224,16 @@
       <c r="A33" s="9">
         <v>30</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="11">
+      <c r="C33" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="8">
         <v>40000</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="8">
         <v>18000</v>
       </c>
     </row>
@@ -1244,16 +1241,16 @@
       <c r="A34" s="9">
         <v>31</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="11">
+      <c r="C34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="8">
         <v>50000</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="8">
         <v>20000</v>
       </c>
     </row>
@@ -1261,33 +1258,33 @@
       <c r="A35" s="9">
         <v>32</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="11">
+      <c r="C35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="8">
         <v>51000</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="8">
         <v>21000</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="12">
+      <c r="A36" s="14">
         <v>33</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="11">
+      <c r="C36" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="8">
         <v>50000</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="8">
         <v>27000</v>
       </c>
     </row>
@@ -1295,84 +1292,84 @@
       <c r="A37" s="9">
         <v>34</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="11">
+      <c r="C37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="8">
         <v>50000</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="8">
         <v>23000</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="13">
+      <c r="A38" s="9">
         <v>35</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="11">
+      <c r="C38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="8">
         <v>50000</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="8">
         <v>23000</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="13">
+      <c r="A39" s="9">
         <v>36</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="11">
+      <c r="C39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="8">
         <v>50000</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="8">
         <v>27000</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="13">
+      <c r="A40" s="9">
         <v>37</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="11">
+      <c r="C40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="8">
         <v>72000</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="8">
         <v>38000</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="14">
+      <c r="A41" s="10">
         <v>38</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="16">
+      <c r="C41" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="12">
         <v>74000</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="12">
         <v>32000</v>
       </c>
     </row>
